--- a/research/traditional_assets/database/data/jamaica/jamaica_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,47 +587,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.0607</v>
-      </c>
-      <c r="E2">
-        <v>0.673</v>
-      </c>
       <c r="G2">
-        <v>0.3070644273989758</v>
+        <v>0.1125909679992025</v>
       </c>
       <c r="H2">
-        <v>0.3070644273989758</v>
+        <v>0.1125909679992025</v>
       </c>
       <c r="I2">
-        <v>0.4243352639935595</v>
+        <v>0.1548100887249526</v>
       </c>
       <c r="J2">
-        <v>0.3785079513511195</v>
+        <v>0.1508746075368604</v>
       </c>
       <c r="K2">
-        <v>23.04</v>
+        <v>16.733</v>
       </c>
       <c r="L2">
-        <v>0.5152402889281481</v>
+        <v>0.1668128800717775</v>
       </c>
       <c r="M2">
-        <v>4.816</v>
+        <v>6.745</v>
       </c>
       <c r="N2">
-        <v>0.02330397754766283</v>
+        <v>0.0393983644859813</v>
       </c>
       <c r="O2">
-        <v>0.2090277777777778</v>
+        <v>0.4030956791967967</v>
       </c>
       <c r="P2">
-        <v>4.816</v>
+        <v>6.745</v>
       </c>
       <c r="Q2">
-        <v>0.02330397754766283</v>
+        <v>0.0393983644859813</v>
       </c>
       <c r="R2">
-        <v>0.2090277777777778</v>
+        <v>0.4030956791967967</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>159.199</v>
+        <v>220.536</v>
       </c>
       <c r="V2">
-        <v>0.7703425916965064</v>
+        <v>1.288177570093458</v>
       </c>
       <c r="W2">
-        <v>0.1041837571780148</v>
+        <v>0.02502998193859121</v>
       </c>
       <c r="X2">
-        <v>0.09055552196189036</v>
+        <v>0.1384723273109282</v>
       </c>
       <c r="Y2">
-        <v>0.0136282352161244</v>
+        <v>-0.113442345372337</v>
       </c>
       <c r="Z2">
-        <v>0.2246464544975007</v>
+        <v>0.4819861809165955</v>
       </c>
       <c r="AA2">
-        <v>0.2089080266433425</v>
+        <v>0.107322826536439</v>
       </c>
       <c r="AB2">
-        <v>0.08640871698240156</v>
+        <v>0.1298630826630939</v>
       </c>
       <c r="AC2">
-        <v>0.1258880095378327</v>
+        <v>-0.02903102486323167</v>
       </c>
       <c r="AD2">
-        <v>153.062</v>
+        <v>204.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>153.062</v>
+        <v>204.4</v>
       </c>
       <c r="AG2">
-        <v>-6.137</v>
+        <v>-16.136</v>
       </c>
       <c r="AH2">
-        <v>0.4255008033981797</v>
+        <v>0.54419595314164</v>
       </c>
       <c r="AI2">
-        <v>0.3952771888323904</v>
+        <v>0.5222092209272025</v>
       </c>
       <c r="AJ2">
-        <v>-0.03060496800865736</v>
+        <v>-0.1040602589898364</v>
       </c>
       <c r="AK2">
-        <v>-0.02691336151700669</v>
+        <v>-0.09442994417069485</v>
       </c>
       <c r="AL2">
-        <v>9.643000000000001</v>
+        <v>11.907</v>
       </c>
       <c r="AM2">
-        <v>9.643000000000001</v>
+        <v>11.907</v>
       </c>
       <c r="AN2">
-        <v>13.57895670688432</v>
+        <v>13.99616543412764</v>
       </c>
       <c r="AO2">
-        <v>1.967748625946282</v>
+        <v>1.30419081212732</v>
       </c>
       <c r="AP2">
-        <v>-0.5444464158977999</v>
+        <v>-1.104902766365379</v>
       </c>
       <c r="AQ2">
-        <v>1.967748625946282</v>
+        <v>1.30419081212732</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SSL Venture Capital Jamaica Limited (JMSE:SSLVC)</t>
+          <t>MFS Capital Partners Limited (JMSE:MFS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,22 +716,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>183</v>
+        <v>2.337349397590361</v>
       </c>
       <c r="H3">
-        <v>183</v>
+        <v>2.337349397590361</v>
       </c>
       <c r="I3">
-        <v>203</v>
+        <v>2.36144578313253</v>
       </c>
       <c r="J3">
-        <v>158.8103658536585</v>
+        <v>2.36144578313253</v>
       </c>
       <c r="K3">
-        <v>1.22</v>
+        <v>0.103</v>
       </c>
       <c r="L3">
-        <v>122</v>
+        <v>1.240963855421687</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,73 +755,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.007</v>
+        <v>0.261</v>
       </c>
       <c r="V3">
-        <v>0.002857142857142857</v>
+        <v>0.0348</v>
       </c>
       <c r="W3">
-        <v>-0.7625</v>
+        <v>-0.3280254777070064</v>
       </c>
       <c r="X3">
-        <v>0.08638829550482388</v>
+        <v>0.1265649223978144</v>
       </c>
       <c r="Y3">
-        <v>-0.8488882955048238</v>
-      </c>
-      <c r="Z3">
-        <v>0.01677852348993288</v>
-      </c>
-      <c r="AA3">
-        <v>2.664603453920445</v>
+        <v>-0.4545904001048207</v>
       </c>
       <c r="AB3">
-        <v>0.08450923059609135</v>
-      </c>
-      <c r="AC3">
-        <v>2.580094223324354</v>
+        <v>0.1265223277956159</v>
       </c>
       <c r="AD3">
-        <v>0.162</v>
+        <v>0.01</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.162</v>
+        <v>0.01</v>
       </c>
       <c r="AG3">
-        <v>0.155</v>
+        <v>-0.251</v>
       </c>
       <c r="AH3">
-        <v>0.06202143950995406</v>
+        <v>0.001331557922769641</v>
       </c>
       <c r="AI3">
-        <v>-0.5934065934065934</v>
+        <v>-0.03623188405797102</v>
       </c>
       <c r="AJ3">
-        <v>0.05950095969289827</v>
+        <v>-0.03462546558145951</v>
       </c>
       <c r="AK3">
-        <v>-0.5535714285714285</v>
+        <v>0.4674115456238362</v>
       </c>
       <c r="AL3">
-        <v>0.051</v>
+        <v>0.008</v>
       </c>
       <c r="AM3">
-        <v>0.051</v>
+        <v>0.008</v>
       </c>
       <c r="AN3">
-        <v>0.07941176470588235</v>
+        <v>0.04901960784313726</v>
       </c>
       <c r="AO3">
-        <v>39.80392156862745</v>
+        <v>24.5</v>
       </c>
       <c r="AP3">
-        <v>0.07598039215686274</v>
+        <v>-1.230392156862745</v>
       </c>
       <c r="AQ3">
-        <v>39.80392156862745</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QWI Investments Limited (JMSE:QWI)</t>
+          <t>Sagicor Select Funds Limited (JMSE:SELECTF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,100 +838,97 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.908355795148248</v>
+        <v>0.9726651480637813</v>
       </c>
       <c r="J4">
-        <v>0.6884532055000171</v>
+        <v>0.9726651480637813</v>
       </c>
       <c r="K4">
-        <v>2.39</v>
+        <v>4.26</v>
       </c>
       <c r="L4">
-        <v>0.6442048517520216</v>
+        <v>0.9703872437357631</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.27</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02061068702290076</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.06338028169014086</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.27</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02061068702290076</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.06338028169014086</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.047</v>
+        <v>0.488</v>
       </c>
       <c r="V4">
-        <v>0.005994897959183673</v>
+        <v>0.03725190839694657</v>
       </c>
       <c r="W4">
-        <v>0.2276190476190476</v>
+        <v>0.1484320557491289</v>
       </c>
       <c r="X4">
-        <v>0.101537751360998</v>
+        <v>0.1264772451526617</v>
       </c>
       <c r="Y4">
-        <v>0.1260812962580496</v>
+        <v>0.0219548105964672</v>
       </c>
       <c r="Z4">
-        <v>0.3122107211983506</v>
+        <v>0.1555909976962608</v>
       </c>
       <c r="AA4">
-        <v>0.2149424718004766</v>
+        <v>0.151337940811625</v>
       </c>
       <c r="AB4">
-        <v>0.08849817620728721</v>
+        <v>0.1264772451526617</v>
       </c>
       <c r="AC4">
-        <v>0.1264442955931894</v>
+        <v>0.02486069565896332</v>
       </c>
       <c r="AD4">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.803</v>
+        <v>-0.488</v>
       </c>
       <c r="AH4">
-        <v>0.2666043030869972</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.1856677524429967</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.2633655924081555</v>
+        <v>-0.03869330796067237</v>
       </c>
       <c r="AK4">
-        <v>0.1831666993399987</v>
+        <v>-0.01999016876945764</v>
       </c>
       <c r="AL4">
-        <v>0.203</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.203</v>
-      </c>
-      <c r="AO4">
-        <v>16.60098522167488</v>
-      </c>
-      <c r="AQ4">
-        <v>16.60098522167488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sagicor Select Funds Limited (JMSE:SELECTF)</t>
+          <t>Proven Investments Limited (JMSE:PROVEN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,40 +948,40 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.115866388308977</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.115866388308977</v>
       </c>
       <c r="I5">
-        <v>0.9642857142857142</v>
+        <v>0.1210855949895616</v>
       </c>
       <c r="J5">
-        <v>0.9642857142857142</v>
+        <v>0.1087729586451174</v>
       </c>
       <c r="K5">
-        <v>6.2</v>
+        <v>12.7</v>
       </c>
       <c r="L5">
-        <v>0.9627329192546583</v>
+        <v>0.1325678496868476</v>
       </c>
       <c r="M5">
-        <v>0.195</v>
+        <v>6.16</v>
       </c>
       <c r="N5">
-        <v>0.01174698795180723</v>
+        <v>0.04268884268884269</v>
       </c>
       <c r="O5">
-        <v>0.0314516129032258</v>
+        <v>0.4850393700787402</v>
       </c>
       <c r="P5">
-        <v>0.195</v>
+        <v>6.16</v>
       </c>
       <c r="Q5">
-        <v>0.01174698795180723</v>
+        <v>0.04268884268884269</v>
       </c>
       <c r="R5">
-        <v>0.0314516129032258</v>
+        <v>0.4850393700787402</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,61 +990,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.485</v>
+        <v>219.5</v>
       </c>
       <c r="V5">
-        <v>0.02921686746987951</v>
+        <v>1.521136521136521</v>
       </c>
       <c r="W5">
-        <v>0.2059800664451827</v>
+        <v>0.07645996387718242</v>
       </c>
       <c r="X5">
-        <v>0.08302001710550982</v>
+        <v>0.2185748087979472</v>
       </c>
       <c r="Y5">
-        <v>0.1229600493396729</v>
+        <v>-0.1421148449207648</v>
       </c>
       <c r="Z5">
-        <v>0.2166453609634663</v>
+        <v>0.5820170109356015</v>
       </c>
       <c r="AA5">
-        <v>0.2089080266433425</v>
+        <v>0.06330771226125304</v>
       </c>
       <c r="AB5">
-        <v>0.08302001710550982</v>
+        <v>0.1462304576466797</v>
       </c>
       <c r="AC5">
-        <v>0.1258880095378327</v>
+        <v>-0.08292274538542665</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>202.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>202.1</v>
       </c>
       <c r="AG5">
-        <v>-0.485</v>
+        <v>-17.40000000000001</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.5834295612009238</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.5723591050693854</v>
       </c>
       <c r="AJ5">
-        <v>-0.03009618367980142</v>
+        <v>-0.1371158392434988</v>
       </c>
       <c r="AK5">
-        <v>-0.01718943824206982</v>
+        <v>-0.1302395209580839</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>11.7</v>
+      </c>
+      <c r="AN5">
+        <v>14.03472222222222</v>
+      </c>
+      <c r="AO5">
+        <v>0.9914529914529915</v>
+      </c>
+      <c r="AP5">
+        <v>-1.208333333333334</v>
+      </c>
+      <c r="AQ5">
+        <v>0.9914529914529915</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Proven Investments Limited (JMSE:PROVEN)</t>
+          <t>QWI Investments Limited (JMSE:QWI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,47 +1075,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.0166</v>
-      </c>
-      <c r="E6">
-        <v>0.304</v>
-      </c>
       <c r="G6">
-        <v>0.3469387755102041</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.3469387755102041</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.2163265306122449</v>
+        <v>-14.51351351351352</v>
       </c>
       <c r="J6">
-        <v>0.2005936920222635</v>
+        <v>-14.51351351351352</v>
       </c>
       <c r="K6">
-        <v>12.7</v>
+        <v>-0.33</v>
       </c>
       <c r="L6">
-        <v>0.3702623906705539</v>
+        <v>-8.918918918918919</v>
       </c>
       <c r="M6">
-        <v>4.3</v>
+        <v>0.315</v>
       </c>
       <c r="N6">
-        <v>0.02461362335432169</v>
+        <v>0.05</v>
       </c>
       <c r="O6">
-        <v>0.3385826771653543</v>
+        <v>-0.9545454545454545</v>
       </c>
       <c r="P6">
-        <v>4.3</v>
+        <v>0.315</v>
       </c>
       <c r="Q6">
-        <v>0.02461362335432169</v>
+        <v>0.05</v>
       </c>
       <c r="R6">
-        <v>0.3385826771653543</v>
+        <v>-0.9545454545454545</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,207 +1118,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>158.5</v>
+        <v>0.287</v>
       </c>
       <c r="V6">
-        <v>0.9072696050372067</v>
+        <v>0.04555555555555555</v>
       </c>
       <c r="W6">
-        <v>0.1041837571780148</v>
+        <v>-0.0264</v>
       </c>
       <c r="X6">
-        <v>0.1265537544574815</v>
+        <v>0.1503797322240421</v>
       </c>
       <c r="Y6">
-        <v>-0.02236999727946679</v>
+        <v>-0.1767797322240421</v>
       </c>
       <c r="Z6">
-        <v>0.2330163043478261</v>
+        <v>0.002417826569953604</v>
       </c>
       <c r="AA6">
-        <v>0.04674160079051383</v>
+        <v>-0.03509115859635366</v>
       </c>
       <c r="AB6">
-        <v>0.09513742216406135</v>
+        <v>0.1332038375305718</v>
       </c>
       <c r="AC6">
-        <v>-0.04839582137354752</v>
+        <v>-0.1682949961269255</v>
       </c>
       <c r="AD6">
-        <v>149.3</v>
+        <v>2.29</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>149.3</v>
+        <v>2.29</v>
       </c>
       <c r="AG6">
-        <v>-9.199999999999989</v>
+        <v>2.003</v>
       </c>
       <c r="AH6">
-        <v>0.4608024691358025</v>
+        <v>0.2665890570430733</v>
       </c>
       <c r="AI6">
-        <v>0.4491576413959086</v>
+        <v>0.1672753834915997</v>
       </c>
       <c r="AJ6">
-        <v>-0.05558912386706942</v>
+        <v>0.2412381067084186</v>
       </c>
       <c r="AK6">
-        <v>-0.05290396779758475</v>
+        <v>0.1494441542938148</v>
       </c>
       <c r="AL6">
-        <v>9.380000000000001</v>
+        <v>0.199</v>
       </c>
       <c r="AM6">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="AN6">
-        <v>16.08836206896552</v>
+        <v>0.199</v>
       </c>
       <c r="AO6">
-        <v>0.7910447761194029</v>
-      </c>
-      <c r="AP6">
-        <v>-0.9913793103448264</v>
+        <v>-2.698492462311558</v>
       </c>
       <c r="AQ6">
-        <v>0.7910447761194029</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Jamaica</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1834 Investments Limited (JMSE:1834)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-0.138</v>
-      </c>
-      <c r="E7">
-        <v>1.042</v>
-      </c>
-      <c r="G7">
-        <v>0.003891050583657588</v>
-      </c>
-      <c r="H7">
-        <v>0.003891050583657588</v>
-      </c>
-      <c r="I7">
-        <v>-0.2140077821011673</v>
-      </c>
-      <c r="J7">
-        <v>-0.212404727553593</v>
-      </c>
-      <c r="K7">
-        <v>0.53</v>
-      </c>
-      <c r="L7">
-        <v>2.062256809338522</v>
-      </c>
-      <c r="M7">
-        <v>0.321</v>
-      </c>
-      <c r="N7">
-        <v>0.06331360946745562</v>
-      </c>
-      <c r="O7">
-        <v>0.6056603773584905</v>
-      </c>
-      <c r="P7">
-        <v>0.321</v>
-      </c>
-      <c r="Q7">
-        <v>0.06331360946745562</v>
-      </c>
-      <c r="R7">
-        <v>0.6056603773584905</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0.16</v>
-      </c>
-      <c r="V7">
-        <v>0.03155818540433925</v>
-      </c>
-      <c r="W7">
-        <v>0.05096153846153846</v>
-      </c>
-      <c r="X7">
-        <v>0.09055552196189036</v>
-      </c>
-      <c r="Y7">
-        <v>-0.0395939835003519</v>
-      </c>
-      <c r="Z7">
-        <v>0.0266321243523316</v>
-      </c>
-      <c r="AA7">
-        <v>-0.005656789117230405</v>
-      </c>
-      <c r="AB7">
-        <v>0.08640871698240156</v>
-      </c>
-      <c r="AC7">
-        <v>-0.09206550609963196</v>
-      </c>
-      <c r="AD7">
-        <v>0.75</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0.75</v>
-      </c>
-      <c r="AG7">
-        <v>0.59</v>
-      </c>
-      <c r="AH7">
-        <v>0.1288659793814433</v>
-      </c>
-      <c r="AI7">
-        <v>0.06787330316742081</v>
-      </c>
-      <c r="AJ7">
-        <v>0.1042402826855124</v>
-      </c>
-      <c r="AK7">
-        <v>0.05417814508723599</v>
-      </c>
-      <c r="AL7">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="AM7">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="AN7">
-        <v>-15.625</v>
-      </c>
-      <c r="AO7">
-        <v>-6.111111111111112</v>
-      </c>
-      <c r="AP7">
-        <v>-12.29166666666667</v>
-      </c>
-      <c r="AQ7">
-        <v>-6.111111111111112</v>
+        <v>-2.698492462311558</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jamaica/jamaica_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_investments_asset_management.xlsx
@@ -588,40 +588,40 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.1125909679992025</v>
+        <v>0.103923584544759</v>
       </c>
       <c r="H2">
-        <v>0.1125909679992025</v>
+        <v>0.103923584544759</v>
       </c>
       <c r="I2">
-        <v>0.1548100887249526</v>
+        <v>0.1004088561591431</v>
       </c>
       <c r="J2">
-        <v>0.1508746075368604</v>
+        <v>0.1004088561591431</v>
       </c>
       <c r="K2">
-        <v>16.733</v>
+        <v>-3.953</v>
       </c>
       <c r="L2">
-        <v>0.1668128800717775</v>
+        <v>-0.02362877773527161</v>
       </c>
       <c r="M2">
-        <v>6.745</v>
+        <v>3.789</v>
       </c>
       <c r="N2">
-        <v>0.0393983644859813</v>
+        <v>0.02627418348242147</v>
       </c>
       <c r="O2">
-        <v>0.4030956791967967</v>
+        <v>-0.9585125221350873</v>
       </c>
       <c r="P2">
-        <v>6.745</v>
+        <v>3.789</v>
       </c>
       <c r="Q2">
-        <v>0.0393983644859813</v>
+        <v>0.02627418348242147</v>
       </c>
       <c r="R2">
-        <v>0.4030956791967967</v>
+        <v>-0.9585125221350873</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>220.536</v>
+        <v>152.359</v>
       </c>
       <c r="V2">
-        <v>1.288177570093458</v>
+        <v>1.056507870466681</v>
       </c>
       <c r="W2">
-        <v>0.02502998193859121</v>
+        <v>-0.01118421052631579</v>
       </c>
       <c r="X2">
-        <v>0.1384723273109282</v>
+        <v>0.1030300929871893</v>
       </c>
       <c r="Y2">
-        <v>-0.113442345372337</v>
+        <v>-0.114214303513505</v>
       </c>
       <c r="Z2">
-        <v>0.4819861809165955</v>
+        <v>0.9096376043280865</v>
       </c>
       <c r="AA2">
-        <v>0.107322826536439</v>
+        <v>-0.02644837939527724</v>
       </c>
       <c r="AB2">
-        <v>0.1298630826630939</v>
+        <v>0.09891792173009704</v>
       </c>
       <c r="AC2">
-        <v>-0.02903102486323167</v>
+        <v>-0.1253518353321146</v>
       </c>
       <c r="AD2">
-        <v>204.4</v>
+        <v>307.667</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>204.4</v>
+        <v>307.667</v>
       </c>
       <c r="AG2">
-        <v>-16.136</v>
+        <v>155.308</v>
       </c>
       <c r="AH2">
-        <v>0.54419595314164</v>
+        <v>0.6808644830341</v>
       </c>
       <c r="AI2">
-        <v>0.5222092209272025</v>
+        <v>0.627948223922148</v>
       </c>
       <c r="AJ2">
-        <v>-0.1040602589898364</v>
+        <v>0.5185264324681654</v>
       </c>
       <c r="AK2">
-        <v>-0.09442994417069485</v>
+        <v>0.4600396330536112</v>
       </c>
       <c r="AL2">
-        <v>11.907</v>
+        <v>18.628</v>
       </c>
       <c r="AM2">
-        <v>11.907</v>
+        <v>18.628</v>
       </c>
       <c r="AN2">
-        <v>13.99616543412764</v>
+        <v>12.87848472164085</v>
       </c>
       <c r="AO2">
-        <v>1.30419081212732</v>
+        <v>0.9017607902082885</v>
       </c>
       <c r="AP2">
-        <v>-1.104902766365379</v>
+        <v>6.500962745918794</v>
       </c>
       <c r="AQ2">
-        <v>1.30419081212732</v>
+        <v>0.9017607902082885</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MFS Capital Partners Limited (JMSE:MFS)</t>
+          <t>PROVEN Group Limited (JMSE:PROVEN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,103 +716,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>2.337349397590361</v>
+        <v>0.103654883163571</v>
       </c>
       <c r="H3">
-        <v>2.337349397590361</v>
+        <v>0.103654883163571</v>
       </c>
       <c r="I3">
-        <v>2.36144578313253</v>
+        <v>0.1078490113840623</v>
       </c>
       <c r="J3">
-        <v>2.36144578313253</v>
+        <v>0.1078490113840623</v>
       </c>
       <c r="K3">
-        <v>0.103</v>
+        <v>-2.86</v>
       </c>
       <c r="L3">
-        <v>1.240963855421687</v>
+        <v>-0.01713600958657879</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>3.31</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02751454696591854</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>-1.157342657342658</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3.31</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02751454696591854</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>-1.157342657342658</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.261</v>
+        <v>151.9</v>
       </c>
       <c r="V3">
-        <v>0.0348</v>
+        <v>1.262676641729011</v>
       </c>
       <c r="W3">
-        <v>-0.3280254777070064</v>
+        <v>-0.0231578947368421</v>
       </c>
       <c r="X3">
-        <v>0.1265649223978144</v>
+        <v>0.2049509245990726</v>
       </c>
       <c r="Y3">
-        <v>-0.4545904001048207</v>
+        <v>-0.2281088193359147</v>
+      </c>
+      <c r="Z3">
+        <v>1.14236824093087</v>
+      </c>
+      <c r="AA3">
+        <v>0.1232032854209446</v>
       </c>
       <c r="AB3">
-        <v>0.1265223277956159</v>
+        <v>0.1116242637745155</v>
+      </c>
+      <c r="AC3">
+        <v>0.01157902164642904</v>
       </c>
       <c r="AD3">
-        <v>0.01</v>
+        <v>305.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.01</v>
+        <v>305.9</v>
       </c>
       <c r="AG3">
-        <v>-0.251</v>
+        <v>154</v>
       </c>
       <c r="AH3">
-        <v>0.001331557922769641</v>
+        <v>0.7177381511027686</v>
       </c>
       <c r="AI3">
-        <v>-0.03623188405797102</v>
+        <v>0.6681957186544343</v>
       </c>
       <c r="AJ3">
-        <v>-0.03462546558145951</v>
+        <v>0.5614290922347794</v>
       </c>
       <c r="AK3">
-        <v>0.4674115456238362</v>
+        <v>0.5034324942791761</v>
       </c>
       <c r="AL3">
-        <v>0.008</v>
+        <v>18.4</v>
       </c>
       <c r="AM3">
-        <v>0.008</v>
+        <v>18.4</v>
       </c>
       <c r="AN3">
-        <v>0.04901960784313726</v>
+        <v>12.79916317991632</v>
       </c>
       <c r="AO3">
-        <v>24.5</v>
+        <v>0.9782608695652175</v>
       </c>
       <c r="AP3">
-        <v>-1.230392156862745</v>
+        <v>6.443514644351463</v>
       </c>
       <c r="AQ3">
-        <v>24.5</v>
+        <v>0.9782608695652175</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sagicor Select Funds Limited (JMSE:SELECTF)</t>
+          <t>QWI Investments Limited (JMSE:QWI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,97 +850,100 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.9726651480637813</v>
+        <v>-0.3207070707070707</v>
       </c>
       <c r="J4">
-        <v>0.9726651480637813</v>
+        <v>-0.3207070707070707</v>
       </c>
       <c r="K4">
-        <v>4.26</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L4">
-        <v>0.9703872437357631</v>
+        <v>0.02272727272727272</v>
       </c>
       <c r="M4">
-        <v>0.27</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.02061068702290076</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.06338028169014086</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.27</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.02061068702290076</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.06338028169014086</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0.488</v>
+        <v>0.014</v>
       </c>
       <c r="V4">
-        <v>0.03725190839694657</v>
+        <v>0.002616822429906542</v>
       </c>
       <c r="W4">
-        <v>0.1484320557491289</v>
+        <v>0.0007894736842105262</v>
       </c>
       <c r="X4">
-        <v>0.1264772451526617</v>
+        <v>0.1100547404999632</v>
       </c>
       <c r="Y4">
-        <v>0.0219548105964672</v>
+        <v>-0.1092652668157527</v>
       </c>
       <c r="Z4">
-        <v>0.1555909976962608</v>
+        <v>0.02954562411400433</v>
       </c>
       <c r="AA4">
-        <v>0.151337940811625</v>
+        <v>-0.009475490561814518</v>
       </c>
       <c r="AB4">
-        <v>0.1264772451526617</v>
+        <v>0.1018535592987418</v>
       </c>
       <c r="AC4">
-        <v>0.02486069565896332</v>
+        <v>-0.1113290498605563</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG4">
-        <v>-0.488</v>
+        <v>1.746</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.2475386779184248</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.1368584758942457</v>
       </c>
       <c r="AJ4">
-        <v>-0.03869330796067237</v>
+        <v>0.246054114994363</v>
       </c>
       <c r="AK4">
-        <v>-0.01999016876945764</v>
+        <v>0.1359177954226997</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.227</v>
+      </c>
+      <c r="AO4">
+        <v>-0.5594713656387665</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.5594713656387665</v>
       </c>
     </row>
     <row r="5">
@@ -939,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Proven Investments Limited (JMSE:PROVEN)</t>
+          <t>Sagicor Select Funds Limited (JMSE:SELECTF)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -947,41 +962,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G5">
-        <v>0.115866388308977</v>
-      </c>
-      <c r="H5">
-        <v>0.115866388308977</v>
-      </c>
-      <c r="I5">
-        <v>0.1210855949895616</v>
-      </c>
-      <c r="J5">
-        <v>0.1087729586451174</v>
-      </c>
       <c r="K5">
-        <v>12.7</v>
-      </c>
-      <c r="L5">
-        <v>0.1325678496868476</v>
+        <v>-1.07</v>
       </c>
       <c r="M5">
-        <v>6.16</v>
+        <v>0.479</v>
       </c>
       <c r="N5">
-        <v>0.04268884268884269</v>
+        <v>0.03742187499999999</v>
       </c>
       <c r="O5">
-        <v>0.4850393700787402</v>
+        <v>-0.4476635514018691</v>
       </c>
       <c r="P5">
-        <v>6.16</v>
+        <v>0.479</v>
       </c>
       <c r="Q5">
-        <v>0.04268884268884269</v>
+        <v>0.03742187499999999</v>
       </c>
       <c r="R5">
-        <v>0.4850393700787402</v>
+        <v>-0.4476635514018691</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -990,73 +990,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>219.5</v>
+        <v>0.388</v>
       </c>
       <c r="V5">
-        <v>1.521136521136521</v>
+        <v>0.0303125</v>
       </c>
       <c r="W5">
-        <v>0.07645996387718242</v>
+        <v>-0.04297188755020081</v>
       </c>
       <c r="X5">
-        <v>0.2185748087979472</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="Y5">
-        <v>-0.1421148449207648</v>
+        <v>-0.1389252401251338</v>
       </c>
       <c r="Z5">
-        <v>0.5820170109356015</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>0.06330771226125304</v>
+        <v>-0.04342126822873997</v>
       </c>
       <c r="AB5">
-        <v>0.1462304576466797</v>
+        <v>0.09595335257493298</v>
       </c>
       <c r="AC5">
-        <v>-0.08292274538542665</v>
+        <v>-0.139374620803673</v>
       </c>
       <c r="AD5">
-        <v>202.1</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>202.1</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-17.40000000000001</v>
+        <v>-0.388</v>
       </c>
       <c r="AH5">
-        <v>0.5834295612009238</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.5723591050693854</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.1371158392434988</v>
+        <v>-0.03126007089912988</v>
       </c>
       <c r="AK5">
-        <v>-0.1302395209580839</v>
+        <v>-0.02019571101394962</v>
       </c>
       <c r="AL5">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>11.7</v>
-      </c>
-      <c r="AN5">
-        <v>14.03472222222222</v>
-      </c>
-      <c r="AO5">
-        <v>0.9914529914529915</v>
-      </c>
-      <c r="AP5">
-        <v>-1.208333333333334</v>
-      </c>
-      <c r="AQ5">
-        <v>0.9914529914529915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1067,7 +1055,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QWI Investments Limited (JMSE:QWI)</t>
+          <t>MFS Capital Partners Limited (JMSE:MFS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1075,110 +1063,89 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>-14.51351351351352</v>
-      </c>
-      <c r="J6">
-        <v>-14.51351351351352</v>
-      </c>
       <c r="K6">
-        <v>-0.33</v>
-      </c>
-      <c r="L6">
-        <v>-8.918918918918919</v>
+        <v>-0.032</v>
       </c>
       <c r="M6">
-        <v>0.315</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0.9545454545454545</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.315</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0.9545454545454545</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>0.287</v>
+        <v>0.057</v>
       </c>
       <c r="V6">
-        <v>0.04555555555555555</v>
+        <v>0.009895833333333335</v>
       </c>
       <c r="W6">
-        <v>-0.0264</v>
+        <v>0.16</v>
       </c>
       <c r="X6">
-        <v>0.1503797322240421</v>
+        <v>0.09600544547441535</v>
       </c>
       <c r="Y6">
-        <v>-0.1767797322240421</v>
-      </c>
-      <c r="Z6">
-        <v>0.002417826569953604</v>
-      </c>
-      <c r="AA6">
-        <v>-0.03509115859635366</v>
+        <v>0.06399455452558465</v>
       </c>
       <c r="AB6">
-        <v>0.1332038375305718</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1682949961269255</v>
+        <v>0.09598228416145228</v>
       </c>
       <c r="AD6">
-        <v>2.29</v>
+        <v>0.007</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.29</v>
+        <v>0.007</v>
       </c>
       <c r="AG6">
-        <v>2.003</v>
+        <v>-0.05</v>
       </c>
       <c r="AH6">
-        <v>0.2665890570430733</v>
+        <v>0.001213802670365875</v>
       </c>
       <c r="AI6">
-        <v>0.1672753834915997</v>
+        <v>-0.02302631578947369</v>
       </c>
       <c r="AJ6">
-        <v>0.2412381067084186</v>
+        <v>-0.008756567425569177</v>
       </c>
       <c r="AK6">
-        <v>0.1494441542938148</v>
+        <v>0.1385041551246537</v>
       </c>
       <c r="AL6">
-        <v>0.199</v>
+        <v>0.001</v>
       </c>
       <c r="AM6">
-        <v>0.199</v>
+        <v>0.001</v>
+      </c>
+      <c r="AN6">
+        <v>-0.7</v>
       </c>
       <c r="AO6">
-        <v>-2.698492462311558</v>
+        <v>-15</v>
+      </c>
+      <c r="AP6">
+        <v>5</v>
       </c>
       <c r="AQ6">
-        <v>-2.698492462311558</v>
+        <v>-15</v>
       </c>
     </row>
   </sheetData>
